--- a/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -1601,25 +1601,19 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
-  </si>
-  <si>
-    <t>識別のための人の名前情報</t>
-  </si>
-  <si>
-    <t>名前が変更されたり、違っていると指摘されたり、コンテキストによって使われる名前が異なる場合がある。名前は、コンテキストに応じて重要性が異なるさまざまなタイプの部分に分割される場合があり、部分への分割は必ずしも重要ではない。個人名の場合、さまざまな部分に暗黙の意味が含まれている場合と含まれていない場合がある。さまざまな文化が名前の部分にさまざまな重要性を関連付けており、システムが世界中の名前の部分を気にする必要がある程度は大きく異なる。</t>
+    <t>A name associated with the contact</t>
+  </si>
+  <si>
+    <t>A name associated with the contact.</t>
   </si>
   <si>
     <t>Need to be able to track the person by name.</t>
   </si>
   <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>ProviderName</t>
+    <t>PID-5, PID-9</t>
+  </si>
+  <si>
+    <t>./name</t>
   </si>
   <si>
     <t>Organization.contact.telecom</t>
@@ -6503,7 +6497,7 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>240</v>
@@ -10179,11 +10173,9 @@
       <c r="M72" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10241,19 +10233,19 @@
         <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>481</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>504</v>
-      </c>
       <c r="AM72" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10261,10 +10253,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10290,14 +10282,14 @@
         <v>313</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10346,7 +10338,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10361,10 +10353,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10375,10 +10367,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10404,14 +10396,14 @@
         <v>366</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10460,7 +10452,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10475,10 +10467,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10489,10 +10481,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10515,19 +10507,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>472</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10576,7 +10568,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -367,7 +367,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -521,7 +521,7 @@
   </si>
   <si>
     <t>医療機関コード（７桁）。Identifier型の拡張「InsuranceOrganizationNo」を使用する。  
-systemには医療機関コードを表すOID「1.2.392.100495.20.3.23」を指定する。  
+systemには医療機関コードを表すOID「http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicalOrganizationID」を指定する。  
 valueには下記の値を格納する。  
 　- 保険医療機関・保険薬局 : `医療機関コード（７桁）`  
 　- 非保険の特定健診・特定保健指導機関 : `機関コード（７桁）`  
@@ -670,7 +670,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -840,10 +840,6 @@
     <t>Organization.identifier:medicalInstitutionCode.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>Organization.identifier:insurerNumber</t>
   </si>
   <si>
@@ -857,7 +853,7 @@
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
-system要素には保険者番号を示すOID"urn:oid:1.2.392.100495.20.3.61"を指定する。</t>
+system要素には保険者番号を示す"http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber"を指定する。</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.id</t>
@@ -875,10 +871,13 @@
     <t>Organization.identifier:insurerNumber.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.61</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.value</t>
+  </si>
+  <si>
+    <t>保険者番号。英数字 券面記載の保険者番号。</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.period</t>
@@ -946,7 +945,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.3.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1588,7 +1587,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.3.0</t>
   </si>
   <si>
     <t>./type</t>
@@ -1655,7 +1654,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.3.0)
 </t>
   </si>
   <si>
@@ -1972,17 +1971,17 @@
   <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.2421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.09765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.0703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1991,26 +1990,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="46.38671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.72265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5469,7 +5468,7 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>240</v>
@@ -5557,13 +5556,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5588,13 +5587,13 @@
         <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>252</v>
@@ -5675,7 +5674,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>181</v>
@@ -5787,7 +5786,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>186</v>
@@ -5901,7 +5900,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>191</v>
@@ -6015,7 +6014,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
@@ -6129,7 +6128,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>210</v>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6245,7 +6244,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>220</v>
@@ -6280,7 +6279,7 @@
         <v>223</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">

--- a/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -268,8 +268,8 @@
     <t>集団行動の何らかの形での達成を目的として結成された、正式または非公式に認められた人々または組織のグループ。企業、機関、企業、部門、コミュニティグループ、医療実践グループ、支払者/保険者などが含まれる。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}org-1:組織は少なくとも名前またはidentifierを持つ必要があり、おそらく1つ以上のものもあるかもしれません / The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -294,13 +294,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -333,13 +333,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -352,19 +352,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -384,13 +384,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -410,19 +410,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -452,8 +452,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -481,8 +481,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:organizationCategory</t>
@@ -536,17 +536,17 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -594,10 +594,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -609,10 +609,13 @@
     <t>Organization.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -621,19 +624,23 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Organization.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -643,6 +650,10 @@
   </si>
   <si>
     <t>Identifier.use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -655,16 +666,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -682,16 +693,16 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -716,13 +727,13 @@
 </t>
   </si>
   <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -747,10 +758,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -772,13 +783,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -810,7 +821,7 @@
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
   <si>
-    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
+    <t>組織は様々なIDで知られている。一部の機関は複数のIDを維持し、ほとんどの機関は組織に関する他の組織との交換のために識別子を収集する。 / Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.id</t>
@@ -846,10 +857,10 @@
     <t>insurerNumber</t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
-  </si>
-  <si>
-    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
+    <t>この組織を複数のシステムで識別する / Identifies this organization  across multiple systems</t>
+  </si>
+  <si>
+    <t>異なる複数のシステム上で組織を識別するために使用される組織のidentifier / Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
@@ -900,14 +911,15 @@
 この要素は、リソースがエラーで作成されたことをマークするために使用される可能性があるため、修飾子としてラベル付けされている。</t>
   </si>
   <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+    <t>このアクティブなフラグは、組織を一時的に閉鎖したり、建設中のマークとして使用するために意図されていません。代わりに、組織内の場所に中断ステータスを設定する必要があります。中断の理由の詳細が必要な場合は、この要素の拡張機能を使用する必要があります。
+この要素は修飾子としてラベル付けされています。これは、リソースが誤って作成されたことを示すために使用できるためです。 / This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
 This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
   </si>
   <si>
     <t>レコードが使用されなくなったことを示すためのフラグが必要で、一般的にUIではユーザのために非表示にする必要がある。</t>
   </si>
   <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+    <t>active要素に値が提供されない場合、このリソースは一般的にアクティブであると見なされる / This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>No equivalent in HL7 v2</t>
@@ -942,7 +954,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>Used to categorize the organization.</t>
+    <t>組織を分類するために使用されます。 / Used to categorize the organization.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type|4.3.0</t>
@@ -1020,8 +1032,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+org-3:組織のテレコムは、家庭で使用することはできません。 / The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-22?</t>
@@ -1036,16 +1048,28 @@
     <t>Organization.telecom.id</t>
   </si>
   <si>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Organization.telecom.extension</t>
   </si>
   <si>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t>Organization.telecom.system</t>
   </si>
   <si>
     <t>phone | fax | email | pager | url | sms | other 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+    <t>連絡先用通信フォーム - どの通信システムを使用するには接点が必要ですか。 / Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
     <t>連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
@@ -1073,16 +1097,16 @@
     <t>Organization.telecom.value</t>
   </si>
   <si>
-    <t>The actual contact point details</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+    <t>実際の連絡先の詳細 / The actual contact point details</t>
+  </si>
+  <si>
+    <t>指定されたコミュニケーションシステムに意味がある形式での実際の連絡先の詳細（電話番号または電子メールアドレス）を提供してください。 / The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
   </si>
   <si>
     <t>連絡先の番号やメールアドレス</t>
   </si>
   <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+    <t>厳密に管理された形式でないレガシー番号をサポートする必要がある。 / Need to support legacy numbers that are not in a tightly controlled format.</t>
   </si>
   <si>
     <t>ContactPoint.value</t>
@@ -1100,7 +1124,7 @@
     <t>work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】homeは使用しないこと。</t>
   </si>
   <si>
-    <t>Identifies the purpose for the contact point.</t>
+    <t>接点の目的を特定する。 / Identifies the purpose for the contact point.</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -1110,7 +1134,7 @@
 　- mobile : モバイル機器</t>
   </si>
   <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+    <t>人がこの連絡先をどのように使用するかを追跡し、ユーザーが目的に適したものを選択できるようにする必要がある。 / Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.3.0</t>
@@ -1135,10 +1159,10 @@
 </t>
   </si>
   <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い） / Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。 / Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -1150,10 +1174,10 @@
     <t>Organization.telecom.period</t>
   </si>
   <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
+    <t>コンタクトポイントが使用されている時間帯 / Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間 / Time period when the contact point was/is in use.</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1188,8 +1212,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+org-2:組織の住所は「家」として使用することはできません。 / An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -1224,13 +1248,13 @@
 　- billing : 請求書、インボイス、領収書などの送付用</t>
   </si>
   <si>
-    <t>Allows an appropriate address to be chosen from a list of many.</t>
+    <t>多くのリストから適切なアドレスを選択できるようにします。 / Allows an appropriate address to be chosen from a list of many.</t>
   </si>
   <si>
     <t>home</t>
   </si>
   <si>
-    <t>The use of an address (home / work / etc.).</t>
+    <t>住所の用途（自宅 / 勤務先など）。 / The use of an address (home / work / etc.).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-use|4.3.0</t>
@@ -1263,7 +1287,7 @@
     <t>both</t>
   </si>
   <si>
-    <t>The type of an address (physical / postal).</t>
+    <t>住所の種類（物理的 / 郵便）。 / The type of an address (physical / postal).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-type|4.3.0</t>
@@ -1292,7 +1316,7 @@
 例：東京都文京区本郷7-3-1</t>
   </si>
   <si>
-    <t>A renderable, unencoded form.</t>
+    <t>レンダリング可能で、不コード化されていないフォーム。 / A renderable, unencoded form.</t>
   </si>
   <si>
     <t>137 Nowhere Street, Erewhon 9132</t>
@@ -1380,7 +1404,7 @@
     <t>地区名 【JP_Patient.address参照】</t>
   </si>
   <si>
-    <t>The name of the administrative area (county).</t>
+    <t>管理エリア（郡）の名前。 / The name of the administrative area (county).</t>
   </si>
   <si>
     <t>【JP Core仕様】日本の住所では使用しない。</t>
@@ -1436,7 +1460,7 @@
     <t>郵便番号 【JP_Patient.address参照】</t>
   </si>
   <si>
-    <t>A postal code designating a region defined by the postal service.</t>
+    <t>郵便サービスによって定義された地域を指定する郵便番号。 / A postal code designating a region defined by the postal service.</t>
   </si>
   <si>
     <t>郵便番号。日本の郵便番号の場合には3桁数字とハイフン1文字と4桁数字からなる半角８文字、または最初の3桁だけの3文字のいずれかとする。 例：113-8655</t>
@@ -1490,7 +1514,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
@@ -1517,7 +1541,7 @@
     <t>参照は、実際のFHIRリソースへの参照である必要があり、内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
   </si>
   <si>
-    <t>Need to be able to track the hierarchy of organizations within an organization.</t>
+    <t>組織内の組織の階層を追跡できる必要がある。 / Need to be able to track the hierarchy of organizations within an organization.</t>
   </si>
   <si>
     <t>.playedBy[classCode=Part].scoper</t>
@@ -1542,7 +1566,7 @@
     <t>より大きな組織内で割り当てられた連絡先を追跡する必要がある。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1562,10 +1586,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1575,16 +1600,16 @@
     <t>Organization.contact.purpose</t>
   </si>
   <si>
-    <t>The type of contact</t>
-  </si>
-  <si>
-    <t>Indicates a purpose for which the contact can be reached.</t>
-  </si>
-  <si>
-    <t>Need to distinguish between multiple contact persons.</t>
-  </si>
-  <si>
-    <t>The purpose for which you would contact a contact party.</t>
+    <t>接触の種類 / The type of contact</t>
+  </si>
+  <si>
+    <t>連絡先に到達できる目的を示しています。 / Indicates a purpose for which the contact can be reached.</t>
+  </si>
+  <si>
+    <t>複数の連絡担当者を区別する必要がある。 / Need to distinguish between multiple contact persons.</t>
+  </si>
+  <si>
+    <t>「連絡を取りたい目的のための連絡先」となります。 / The purpose for which you would contact a contact party.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.3.0</t>
@@ -1600,13 +1625,13 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the contact</t>
-  </si>
-  <si>
-    <t>A name associated with the contact.</t>
-  </si>
-  <si>
-    <t>Need to be able to track the person by name.</t>
+    <t>コンタクトに関連する名前 / A name associated with the contact</t>
+  </si>
+  <si>
+    <t>連絡関係にある名前 / A name associated with the contact.</t>
+  </si>
+  <si>
+    <t>名前で人を追跡できる必要がある。 / Need to be able to track the person by name.</t>
   </si>
   <si>
     <t>PID-5, PID-9</t>
@@ -1618,13 +1643,13 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>Contact details (telephone, email, etc.)  for a contact</t>
-  </si>
-  <si>
-    <t>A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
-  </si>
-  <si>
-    <t>People have (primary) ways to contact them in some way such as phone, email.</t>
+    <t>連絡先詳細（電話、メールなど）連絡先のため / Contact details (telephone, email, etc.)  for a contact</t>
+  </si>
+  <si>
+    <t>当該のパーティーと連絡を取るための連絡先情報（例：電話番号やメールアドレス） / A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
+  </si>
+  <si>
+    <t>人には電話やメールなど（主な）連絡方法がある。 / People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
     <t>PID-13, PID-14</t>
@@ -1636,13 +1661,13 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t>Visiting or postal addresses for the contact</t>
-  </si>
-  <si>
-    <t>Visiting or postal addresses for the contact.</t>
-  </si>
-  <si>
-    <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
+    <t>連絡のための訪問先または郵送先の住所 / Visiting or postal addresses for the contact</t>
+  </si>
+  <si>
+    <t>連絡先の訪問または郵便送付先 / Visiting or postal addresses for the contact.</t>
+  </si>
+  <si>
+    <t>連絡先の住所を連絡、請求、または報告要件のために追跡する必要がある場合がある。 / May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
   </si>
   <si>
     <t>PID-11</t>
@@ -1995,7 +2020,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="46.38671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="70.55078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3765,7 +3790,7 @@
         <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3806,7 +3831,7 @@
         <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
@@ -3815,7 +3840,7 @@
         <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3827,7 +3852,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3844,10 +3869,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3873,16 +3898,16 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3907,11 +3932,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3929,7 +3954,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3941,13 +3966,13 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3958,10 +3983,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3984,19 +4009,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4021,11 +4046,11 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
@@ -4043,7 +4068,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4055,13 +4080,13 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4072,10 +4097,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4101,16 +4126,16 @@
         <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4123,7 +4148,7 @@
         <v>78</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>78</v>
@@ -4159,7 +4184,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4171,16 +4196,16 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4188,10 +4213,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4214,16 +4239,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4237,7 +4262,7 @@
         <v>78</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>78</v>
@@ -4273,7 +4298,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4285,16 +4310,16 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -4302,10 +4327,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4328,13 +4353,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4385,7 +4410,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4397,16 +4422,16 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4414,10 +4439,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4440,16 +4465,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4499,7 +4524,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4511,16 +4536,16 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4528,13 +4553,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4559,16 +4584,16 @@
         <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4646,7 +4671,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>181</v>
@@ -4758,7 +4783,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>186</v>
@@ -4793,7 +4818,7 @@
         <v>188</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4834,7 +4859,7 @@
         <v>138</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
@@ -4843,7 +4868,7 @@
         <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4855,7 +4880,7 @@
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
@@ -4872,10 +4897,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4901,16 +4926,16 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4935,11 +4960,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4957,7 +4982,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4969,13 +4994,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4986,10 +5011,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5012,19 +5037,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5049,11 +5074,11 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5071,7 +5096,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5083,13 +5108,13 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5100,10 +5125,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5129,29 +5154,29 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -5187,7 +5212,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5199,16 +5224,16 @@
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5216,10 +5241,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5242,16 +5267,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5265,7 +5290,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -5301,7 +5326,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5313,16 +5338,16 @@
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5330,10 +5355,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5356,13 +5381,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5413,7 +5438,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5425,16 +5450,16 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5442,10 +5467,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5468,16 +5493,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5527,7 +5552,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5539,16 +5564,16 @@
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5556,13 +5581,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5587,16 +5612,16 @@
         <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5674,7 +5699,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>181</v>
@@ -5786,7 +5811,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>186</v>
@@ -5821,7 +5846,7 @@
         <v>188</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5862,7 +5887,7 @@
         <v>138</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>78</v>
@@ -5871,7 +5896,7 @@
         <v>139</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5883,7 +5908,7 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5900,10 +5925,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5929,16 +5954,16 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5963,11 +5988,11 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -5985,7 +6010,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5997,13 +6022,13 @@
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6014,10 +6039,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6040,19 +6065,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6077,11 +6102,11 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -6099,7 +6124,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6111,13 +6136,13 @@
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6128,10 +6153,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6157,29 +6182,29 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -6215,7 +6240,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6227,16 +6252,16 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6244,10 +6269,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6270,16 +6295,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6293,7 +6318,7 @@
         <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>78</v>
@@ -6329,7 +6354,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6341,16 +6366,16 @@
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6358,10 +6383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6384,13 +6409,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6441,7 +6466,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6453,16 +6478,16 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6470,10 +6495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6496,16 +6521,16 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6555,7 +6580,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6567,16 +6592,16 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6584,10 +6609,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6610,70 +6635,70 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6688,24 +6713,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6728,19 +6753,19 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6765,13 +6790,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6789,7 +6814,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6804,24 +6829,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>185</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6844,19 +6869,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6905,7 +6930,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6920,13 +6945,13 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6934,10 +6959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6960,19 +6985,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7021,7 +7046,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7039,7 +7064,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7050,10 +7075,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7076,19 +7101,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7137,7 +7162,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7146,19 +7171,19 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7166,10 +7191,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7195,10 +7220,10 @@
         <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>182</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>183</v>
+        <v>328</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7278,10 +7303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7307,10 +7332,10 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>166</v>
@@ -7354,7 +7379,7 @@
         <v>138</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7363,7 +7388,7 @@
         <v>139</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7392,10 +7417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7421,13 +7446,13 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7453,11 +7478,11 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7475,7 +7500,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7484,19 +7509,19 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7504,10 +7529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7530,19 +7555,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7591,7 +7616,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7606,13 +7631,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7620,10 +7645,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7649,16 +7674,16 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7683,11 +7708,11 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7705,7 +7730,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7720,13 +7745,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7734,10 +7759,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7760,16 +7785,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7819,7 +7844,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7848,10 +7873,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7874,16 +7899,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7933,7 +7958,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7951,10 +7976,10 @@
         <v>133</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7962,10 +7987,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7988,19 +8013,19 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8049,7 +8074,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8058,19 +8083,19 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8078,10 +8103,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8190,10 +8215,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8225,7 +8250,7 @@
         <v>188</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8266,7 +8291,7 @@
         <v>138</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
@@ -8275,7 +8300,7 @@
         <v>139</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8287,7 +8312,7 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -8304,10 +8329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8333,16 +8358,16 @@
         <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8355,7 +8380,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8367,13 +8392,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8391,7 +8416,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8403,16 +8428,16 @@
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8420,10 +8445,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8449,13 +8474,13 @@
         <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8469,7 +8494,7 @@
         <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8481,13 +8506,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8505,7 +8530,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8517,13 +8542,13 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8534,10 +8559,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8560,19 +8585,19 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8585,7 +8610,7 @@
         <v>78</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>78</v>
@@ -8621,7 +8646,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8633,13 +8658,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8650,10 +8675,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8676,16 +8701,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8699,7 +8724,7 @@
         <v>78</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>78</v>
@@ -8735,7 +8760,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8747,16 +8772,16 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8764,14 +8789,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8790,16 +8815,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8813,7 +8838,7 @@
         <v>78</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>78</v>
@@ -8849,7 +8874,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8861,16 +8886,16 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8878,14 +8903,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8904,16 +8929,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8927,7 +8952,7 @@
         <v>78</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>78</v>
@@ -8963,7 +8988,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8975,13 +9000,13 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -8992,14 +9017,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9018,16 +9043,16 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9077,7 +9102,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9089,16 +9114,16 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9106,14 +9131,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9132,16 +9157,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9155,7 +9180,7 @@
         <v>78</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>78</v>
@@ -9191,7 +9216,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9203,16 +9228,16 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9220,10 +9245,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9246,16 +9271,16 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9305,7 +9330,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9317,16 +9342,16 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9334,10 +9359,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9360,19 +9385,19 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9385,7 +9410,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -9421,7 +9446,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9433,16 +9458,16 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9450,10 +9475,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9476,19 +9501,19 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9537,7 +9562,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9552,10 +9577,10 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>185</v>
@@ -9566,10 +9591,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9592,19 +9617,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9653,7 +9678,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9665,13 +9690,13 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9682,10 +9707,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9708,13 +9733,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>182</v>
+        <v>327</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>183</v>
+        <v>328</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9794,10 +9819,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9823,10 +9848,10 @@
         <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>166</v>
@@ -9879,7 +9904,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9908,14 +9933,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9937,10 +9962,10 @@
         <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>166</v>
@@ -9995,7 +10020,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10024,10 +10049,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10050,17 +10075,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10085,13 +10110,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10109,7 +10134,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10127,7 +10152,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10138,10 +10163,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10164,17 +10189,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10223,7 +10248,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10238,10 +10263,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10252,10 +10277,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10278,17 +10303,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10337,7 +10362,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10352,10 +10377,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10366,10 +10391,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10392,17 +10417,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10451,7 +10476,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10466,10 +10491,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10480,10 +10505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10506,19 +10531,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10567,7 +10592,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
